--- a/public/templates/items-import-template.xlsx
+++ b/public/templates/items-import-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\The Web Developer Bootcamp 2024\JAVASCRIPT COURSE\Projects\Sarathi\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE8B9AC-B5B2-4B84-A9E1-FBD13CBDBF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB356E4-70AD-4CF3-85CA-2962D43CCB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{1FDA126F-B6EF-4CEF-AEDD-3485C1435921}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
   <si>
     <t>name</t>
   </si>
@@ -57,9 +57,6 @@
     <t>vatExempt</t>
   </si>
   <si>
-    <t>mainUnit</t>
-  </si>
-  <si>
     <t>hscode</t>
   </si>
   <si>
@@ -82,6 +79,12 @@
   </si>
   <si>
     <t>Sample Item 5</t>
+  </si>
+  <si>
+    <t>itemscompany</t>
+  </si>
+  <si>
+    <t>mainunit</t>
   </si>
 </sst>
 </file>
@@ -446,49 +449,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30596A1E-ADE3-4EE5-B0BF-25EC3C1D7EE4}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="B2" s="1">
         <v>9018</v>
@@ -497,24 +504,27 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="B3" s="1">
         <v>9018</v>
@@ -523,24 +533,27 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>14</v>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1">
         <v>9018</v>
@@ -549,24 +562,27 @@
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
         <v>9018</v>
@@ -575,24 +591,27 @@
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
         <v>9018</v>
@@ -601,19 +620,22 @@
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>14</v>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
